--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,29 +8,41 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DD6A77-DA2A-41FE-8872-14B3C56557AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9BF93-E57C-471A-81CF-61AF1D20B662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company" sheetId="5" r:id="rId1"/>
     <sheet name="ProjectContract" sheetId="6" r:id="rId2"/>
     <sheet name="Persons" sheetId="2" r:id="rId3"/>
+    <sheet name="Passports" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
   <si>
     <t>aýaly</t>
   </si>
@@ -201,18 +213,65 @@
   </si>
   <si>
     <t>NameTm</t>
+  </si>
+  <si>
+    <t>Passport Number</t>
+  </si>
+  <si>
+    <t>Personal Number</t>
+  </si>
+  <si>
+    <t>Authority</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Expiration Date</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Passport Type</t>
+  </si>
+  <si>
+    <t>Issued Country</t>
+  </si>
+  <si>
+    <t>P00000010</t>
+  </si>
+  <si>
+    <t>PN010101</t>
+  </si>
+  <si>
+    <t>Demo auth</t>
+  </si>
+  <si>
+    <t>P - MILLI PASPORT</t>
+  </si>
+  <si>
+    <t>Gwadelupa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -289,22 +348,24 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -801,7 +862,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -918,4 +979,76 @@
     <oddHeader>&amp;L&amp;"Aptos"&amp;9&amp;KFFFF00 Şirket İçi&amp;1#_x000D_</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" customWidth="1"/>
+    <col min="6" max="6" width="16.7265625" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="9">
+        <v>43961</v>
+      </c>
+      <c r="E2" s="9">
+        <v>47644</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9BF93-E57C-471A-81CF-61AF1D20B662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5A6D9A-11EB-44B2-B44B-73C21F4BDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Company" sheetId="5" r:id="rId1"/>
-    <sheet name="ProjectContract" sheetId="6" r:id="rId2"/>
-    <sheet name="Persons" sheetId="2" r:id="rId3"/>
-    <sheet name="Passports" sheetId="7" r:id="rId4"/>
+    <sheet name="Persons" sheetId="2" r:id="rId1"/>
+    <sheet name="Passports" sheetId="7" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
   <si>
     <t>aýaly</t>
   </si>
@@ -168,51 +166,6 @@
   </si>
   <si>
     <t>First Name</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>TaxInformation</t>
-  </si>
-  <si>
-    <t>TRM-2026-</t>
-  </si>
-  <si>
-    <t>TAX000000</t>
-  </si>
-  <si>
-    <t>demo@company.com</t>
-  </si>
-  <si>
-    <t>Demo Company Address</t>
-  </si>
-  <si>
-    <t>IsDefault</t>
-  </si>
-  <si>
-    <t>ApplicationNumberPadding</t>
-  </si>
-  <si>
-    <t>AppNumberPrefix</t>
-  </si>
-  <si>
-    <t>Atçylyk</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>NameTm</t>
   </si>
   <si>
     <t>Passport Number</t>
@@ -352,7 +305,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -362,8 +315,6 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -648,130 +599,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E5945E-8BD6-43C0-92AF-55795FB162AB}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="8" width="26.6328125" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="7">
-        <v>99300000000</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="7">
-        <v>3</v>
-      </c>
-      <c r="H2" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{45DA98CD-C2C6-419E-813E-003B7CEC4E59}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8152C4B4-2584-4486-B184-7B26F12B6A99}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="5" width="14.453125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="21.54296875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1560</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18289B1E-BB40-4235-8E6A-EF150566973D}">
   <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -862,7 +689,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -981,7 +808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -998,54 +825,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="9">
+        <v>52</v>
+      </c>
+      <c r="D2" s="7">
         <v>43961</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>47644</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5A6D9A-11EB-44B2-B44B-73C21F4BDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB439F-7C42-484C-B74A-0A535B19D1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="28800" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
     <sheet name="Passports" sheetId="7" r:id="rId2"/>
+    <sheet name="Education" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>aýaly</t>
   </si>
@@ -205,6 +206,33 @@
   </si>
   <si>
     <t>Gwadelupa</t>
+  </si>
+  <si>
+    <t>Graduation Year</t>
+  </si>
+  <si>
+    <t>Education Level</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Ýokary</t>
+  </si>
+  <si>
+    <t>Hitit uniwersiteti</t>
+  </si>
+  <si>
+    <t>Ekwador</t>
+  </si>
+  <si>
+    <t>Termo Elektrostansiýa</t>
   </si>
 </sst>
 </file>
@@ -878,4 +906,62 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8908F50A-91BA-4FB7-ACAF-C045C8FDC603}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB439F-7C42-484C-B74A-0A535B19D1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2799A29-3F66-4FF3-BEEB-E91387AAF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="3380" windowWidth="28800" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
     <sheet name="Passports" sheetId="7" r:id="rId2"/>
     <sheet name="Education" sheetId="8" r:id="rId3"/>
+    <sheet name="MedicalRecords" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>aýaly</t>
   </si>
@@ -233,6 +234,21 @@
   </si>
   <si>
     <t>Termo Elektrostansiýa</t>
+  </si>
+  <si>
+    <t>Document Number</t>
+  </si>
+  <si>
+    <t>Is Active</t>
+  </si>
+  <si>
+    <t>Validity Duration</t>
+  </si>
+  <si>
+    <t>MR0001</t>
+  </si>
+  <si>
+    <t>3 aý</t>
   </si>
 </sst>
 </file>
@@ -964,4 +980,62 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B482E7A6-8550-4143-8677-7DF7C1431F64}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46199</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2799A29-3F66-4FF3-BEEB-E91387AAF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99F6BDB-3467-4014-8991-28BEC1E840D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4060" yWindow="4060" windowWidth="28800" windowHeight="15370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
     <sheet name="Passports" sheetId="7" r:id="rId2"/>
     <sheet name="Education" sheetId="8" r:id="rId3"/>
     <sheet name="MedicalRecords" sheetId="9" r:id="rId4"/>
+    <sheet name="Lodging" sheetId="10" r:id="rId5"/>
+    <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
   <si>
     <t>aýaly</t>
   </si>
@@ -249,6 +251,45 @@
   </si>
   <si>
     <t>3 aý</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Full Address</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo Lodge full address </t>
+  </si>
+  <si>
+    <t>Demo Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Lodging</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Demo Lodge full address</t>
+  </si>
+  <si>
+    <t>Lebap welaýaty</t>
+  </si>
+  <si>
+    <t>Atamyrat şäheri</t>
   </si>
 </sst>
 </file>
@@ -1038,4 +1079,117 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D0BDE8-D87C-418C-AFC3-DBF6850B63AF}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324BC0BB-CC40-4196-829B-1D1F4666C8A9}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.90625" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="19.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99F6BDB-3467-4014-8991-28BEC1E840D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43F9D9A-CB6C-4592-B477-72433B4F0455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4060" yWindow="4060" windowWidth="28800" windowHeight="15370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4400" yWindow="4400" windowWidth="28800" windowHeight="15370" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="MedicalRecords" sheetId="9" r:id="rId4"/>
     <sheet name="Lodging" sheetId="10" r:id="rId5"/>
     <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
+    <sheet name="PositionHistory" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
   <si>
     <t>aýaly</t>
   </si>
@@ -290,6 +291,21 @@
   </si>
   <si>
     <t>Atamyrat şäheri</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Administratiw işleriniň ýolbaşçysy</t>
+  </si>
+  <si>
+    <t>PROJE OFİSİ</t>
   </si>
 </sst>
 </file>
@@ -1192,4 +1208,55 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE0BD76-03FB-4C51-8FBE-60A5DA5A106E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="32.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B2" s="7">
+        <v>47601</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43F9D9A-CB6C-4592-B477-72433B4F0455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAA47E5-DA55-42D3-B617-23B20788E796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4400" yWindow="4400" windowWidth="28800" windowHeight="15370" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="4740" windowWidth="28800" windowHeight="15370" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
   <si>
     <t>aýaly</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>PROJE OFİSİ</t>
+  </si>
+  <si>
+    <t>My Lodging</t>
   </si>
 </sst>
 </file>
@@ -1123,8 +1126,8 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="s">
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAA47E5-DA55-42D3-B617-23B20788E796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B235C8F-186C-4B27-83C8-D5EC6DEB5147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="4740" windowWidth="28800" windowHeight="15370" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="4740" windowWidth="28800" windowHeight="15370" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Lodging" sheetId="10" r:id="rId5"/>
     <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
     <sheet name="PositionHistory" sheetId="12" r:id="rId7"/>
+    <sheet name="EmployeeContracts" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
   <si>
     <t>aýaly</t>
   </si>
@@ -309,6 +310,12 @@
   </si>
   <si>
     <t>My Lodging</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Position History</t>
   </si>
 </sst>
 </file>
@@ -1262,4 +1269,55 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BD487E-2A04-4D39-924D-AA315766A8E7}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="34.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>44134</v>
+      </c>
+      <c r="C2">
+        <v>10000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9BF93-E57C-471A-81CF-61AF1D20B662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B235C8F-186C-4B27-83C8-D5EC6DEB5147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="4740" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Company" sheetId="5" r:id="rId1"/>
-    <sheet name="ProjectContract" sheetId="6" r:id="rId2"/>
-    <sheet name="Persons" sheetId="2" r:id="rId3"/>
-    <sheet name="Passports" sheetId="7" r:id="rId4"/>
+    <sheet name="Persons" sheetId="2" r:id="rId1"/>
+    <sheet name="Passports" sheetId="7" r:id="rId2"/>
+    <sheet name="Education" sheetId="8" r:id="rId3"/>
+    <sheet name="MedicalRecords" sheetId="9" r:id="rId4"/>
+    <sheet name="Lodging" sheetId="10" r:id="rId5"/>
+    <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
+    <sheet name="PositionHistory" sheetId="12" r:id="rId7"/>
+    <sheet name="EmployeeContracts" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
   <si>
     <t>aýaly</t>
   </si>
@@ -170,88 +174,148 @@
     <t>First Name</t>
   </si>
   <si>
+    <t>Passport Number</t>
+  </si>
+  <si>
+    <t>Personal Number</t>
+  </si>
+  <si>
+    <t>Authority</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Expiration Date</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Passport Type</t>
+  </si>
+  <si>
+    <t>Issued Country</t>
+  </si>
+  <si>
+    <t>P00000010</t>
+  </si>
+  <si>
+    <t>PN010101</t>
+  </si>
+  <si>
+    <t>Demo auth</t>
+  </si>
+  <si>
+    <t>P - MILLI PASPORT</t>
+  </si>
+  <si>
+    <t>Gwadelupa</t>
+  </si>
+  <si>
+    <t>Graduation Year</t>
+  </si>
+  <si>
+    <t>Education Level</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Ýokary</t>
+  </si>
+  <si>
+    <t>Hitit uniwersiteti</t>
+  </si>
+  <si>
+    <t>Ekwador</t>
+  </si>
+  <si>
+    <t>Termo Elektrostansiýa</t>
+  </si>
+  <si>
+    <t>Document Number</t>
+  </si>
+  <si>
+    <t>Is Active</t>
+  </si>
+  <si>
+    <t>Validity Duration</t>
+  </si>
+  <si>
+    <t>MR0001</t>
+  </si>
+  <si>
+    <t>3 aý</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>TaxInformation</t>
-  </si>
-  <si>
-    <t>TRM-2026-</t>
-  </si>
-  <si>
-    <t>TAX000000</t>
-  </si>
-  <si>
-    <t>demo@company.com</t>
-  </si>
-  <si>
-    <t>Demo Company Address</t>
-  </si>
-  <si>
-    <t>IsDefault</t>
-  </si>
-  <si>
-    <t>ApplicationNumberPadding</t>
-  </si>
-  <si>
-    <t>AppNumberPrefix</t>
-  </si>
-  <si>
-    <t>Atçylyk</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>NameTm</t>
-  </si>
-  <si>
-    <t>Passport Number</t>
-  </si>
-  <si>
-    <t>Personal Number</t>
-  </si>
-  <si>
-    <t>Authority</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Expiration Date</t>
-  </si>
-  <si>
-    <t>Person</t>
-  </si>
-  <si>
-    <t>Passport Type</t>
-  </si>
-  <si>
-    <t>Issued Country</t>
-  </si>
-  <si>
-    <t>P00000010</t>
-  </si>
-  <si>
-    <t>PN010101</t>
-  </si>
-  <si>
-    <t>Demo auth</t>
-  </si>
-  <si>
-    <t>P - MILLI PASPORT</t>
-  </si>
-  <si>
-    <t>Gwadelupa</t>
+    <t>Full Address</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo Lodge full address </t>
+  </si>
+  <si>
+    <t>Demo Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Lodging</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Demo Lodge full address</t>
+  </si>
+  <si>
+    <t>Lebap welaýaty</t>
+  </si>
+  <si>
+    <t>Atamyrat şäheri</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Administratiw işleriniň ýolbaşçysy</t>
+  </si>
+  <si>
+    <t>PROJE OFİSİ</t>
+  </si>
+  <si>
+    <t>My Lodging</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Position History</t>
   </si>
 </sst>
 </file>
@@ -352,7 +416,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -362,8 +426,6 @@
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -648,130 +710,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E5945E-8BD6-43C0-92AF-55795FB162AB}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="8" width="26.6328125" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="7">
-        <v>99300000000</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="7">
-        <v>3</v>
-      </c>
-      <c r="H2" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{45DA98CD-C2C6-419E-813E-003B7CEC4E59}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8152C4B4-2584-4486-B184-7B26F12B6A99}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="5" width="14.453125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="21.54296875" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1560</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18289B1E-BB40-4235-8E6A-EF150566973D}">
   <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -862,7 +800,7 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -981,7 +919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -998,54 +936,385 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="9">
+        <v>52</v>
+      </c>
+      <c r="D2" s="7">
         <v>43961</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>47644</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8908F50A-91BA-4FB7-ACAF-C045C8FDC603}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B482E7A6-8550-4143-8677-7DF7C1431F64}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46199</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>68</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D0BDE8-D87C-418C-AFC3-DBF6850B63AF}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324BC0BB-CC40-4196-829B-1D1F4666C8A9}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.90625" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="20.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="19.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE0BD76-03FB-4C51-8FBE-60A5DA5A106E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="32.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B2" s="7">
+        <v>47601</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BD487E-2A04-4D39-924D-AA315766A8E7}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="34.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>44134</v>
+      </c>
+      <c r="C2">
+        <v>10000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B235C8F-186C-4B27-83C8-D5EC6DEB5147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F112BA35-8445-473C-A284-F49D879A6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="4740" windowWidth="28800" windowHeight="15370" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3570" yWindow="3470" windowWidth="28800" windowHeight="15370" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
     <sheet name="PositionHistory" sheetId="12" r:id="rId7"/>
     <sheet name="EmployeeContracts" sheetId="13" r:id="rId8"/>
+    <sheet name="CompanyHead" sheetId="14" r:id="rId9"/>
+    <sheet name="Representative" sheetId="15" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>aýaly</t>
   </si>
@@ -316,6 +318,12 @@
   </si>
   <si>
     <t>Position History</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Is Local</t>
   </si>
 </sst>
 </file>
@@ -919,6 +927,42 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8924C1-D194-4DF1-A42A-3D3D75E0E381}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.90625" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>
@@ -1320,4 +1364,47 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B9BD19-C4E6-4DD0-A060-40ED3F97C71A}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="35.26953125" customWidth="1"/>
+    <col min="4" max="4" width="23.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F112BA35-8445-473C-A284-F49D879A6D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F964ABAA-70D6-42E0-AB6E-D8DBDE4A52B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="3470" windowWidth="28800" windowHeight="15370" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="EmployeeContracts" sheetId="13" r:id="rId8"/>
     <sheet name="CompanyHead" sheetId="14" r:id="rId9"/>
     <sheet name="Representative" sheetId="15" r:id="rId10"/>
+    <sheet name="Applications" sheetId="16" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="113">
   <si>
     <t>aýaly</t>
   </si>
@@ -324,13 +325,76 @@
   </si>
   <si>
     <t>Is Local</t>
+  </si>
+  <si>
+    <t>Application Number</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Application Type</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Visa Category</t>
+  </si>
+  <si>
+    <t>Migration Service</t>
+  </si>
+  <si>
+    <t>Urgency</t>
+  </si>
+  <si>
+    <t>Visa Period</t>
+  </si>
+  <si>
+    <t>Visa Type</t>
+  </si>
+  <si>
+    <t>Company Head</t>
+  </si>
+  <si>
+    <t>Representative</t>
+  </si>
+  <si>
+    <t>TRM-2026-</t>
+  </si>
+  <si>
+    <t>App_Inv_And_WP</t>
+  </si>
+  <si>
+    <t>InvitationAndWorkPermit</t>
+  </si>
+  <si>
+    <t>Köp gezeklik</t>
+  </si>
+  <si>
+    <t>Adaty tertipde !</t>
+  </si>
+  <si>
+    <t>6 (alty) aý</t>
+  </si>
+  <si>
+    <t>WP-Işçi Wiza</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +443,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -424,7 +497,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -436,6 +509,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -963,6 +1037,128 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A61E3F-9A82-457E-8587-FCB3F1FC8E8F}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.90625" customWidth="1"/>
+    <col min="8" max="8" width="16.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.54296875" customWidth="1"/>
+    <col min="10" max="10" width="22.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.90625" customWidth="1"/>
+    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="13" max="13" width="15.1796875" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.7265625" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="15.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F964ABAA-70D6-42E0-AB6E-D8DBDE4A52B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA6A749-75F0-498D-AAD3-9497A0AAE339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="CompanyHead" sheetId="14" r:id="rId9"/>
     <sheet name="Representative" sheetId="15" r:id="rId10"/>
     <sheet name="Applications" sheetId="16" r:id="rId11"/>
+    <sheet name="ApplicationItems" sheetId="17" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
   <si>
     <t>aýaly</t>
   </si>
@@ -388,6 +389,12 @@
   </si>
   <si>
     <t>WP-Işçi Wiza</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>TRM-2026-1</t>
   </si>
 </sst>
 </file>
@@ -1159,6 +1166,36 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38529E09-C163-4F91-A321-7C547851DA34}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA6A749-75F0-498D-AAD3-9497A0AAE339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3E3FD8-0785-4F54-B1FD-A62D625C7BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="Representative" sheetId="15" r:id="rId10"/>
     <sheet name="Applications" sheetId="16" r:id="rId11"/>
     <sheet name="ApplicationItems" sheetId="17" r:id="rId12"/>
+    <sheet name="Invitations" sheetId="18" r:id="rId13"/>
+    <sheet name="InvitationItems" sheetId="19" r:id="rId14"/>
+    <sheet name="Sheet3" sheetId="20" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="120">
   <si>
     <t>aýaly</t>
   </si>
@@ -395,6 +398,21 @@
   </si>
   <si>
     <t>TRM-2026-1</t>
+  </si>
+  <si>
+    <t>Invitation Number</t>
+  </si>
+  <si>
+    <t>Is Cancelled</t>
+  </si>
+  <si>
+    <t>INV0001</t>
+  </si>
+  <si>
+    <t>Is Used</t>
+  </si>
+  <si>
+    <t>Is Changed</t>
   </si>
 </sst>
 </file>
@@ -1196,6 +1214,119 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED124FB3-4077-4682-BFCE-D98F2F0089BC}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18967DE7-069E-4DE5-89BC-8EF82DB3AC0C}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" customWidth="1"/>
+    <col min="6" max="6" width="11.08984375" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2AFAE0-31A3-4E30-9723-0089076DBD4C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
   <dimension ref="A1:H2"/>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3E3FD8-0785-4F54-B1FD-A62D625C7BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7319697-A3B5-46BC-A07E-C0F9D25BB2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="7" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,9 @@
     <sheet name="ApplicationItems" sheetId="17" r:id="rId12"/>
     <sheet name="Invitations" sheetId="18" r:id="rId13"/>
     <sheet name="InvitationItems" sheetId="19" r:id="rId14"/>
-    <sheet name="Sheet3" sheetId="20" r:id="rId15"/>
+    <sheet name="WorkPermits" sheetId="20" r:id="rId15"/>
+    <sheet name="WorkPermitItems" sheetId="21" r:id="rId16"/>
+    <sheet name="WorkPermitItemCities" sheetId="22" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="128">
   <si>
     <t>aýaly</t>
   </si>
@@ -413,6 +415,30 @@
   </si>
   <si>
     <t>Is Changed</t>
+  </si>
+  <si>
+    <t>Work Permit Number</t>
+  </si>
+  <si>
+    <t>WP0001</t>
+  </si>
+  <si>
+    <t>Item Number</t>
+  </si>
+  <si>
+    <t>AS Number</t>
+  </si>
+  <si>
+    <t>Is Extended</t>
+  </si>
+  <si>
+    <t>WP0001/1</t>
+  </si>
+  <si>
+    <t>AS000045</t>
+  </si>
+  <si>
+    <t>Akbudaý etraby</t>
   </si>
 </sst>
 </file>
@@ -1320,9 +1346,160 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2AFAE0-31A3-4E30-9723-0089076DBD4C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976BFC1-7B18-4C48-8C10-5F11DE69F168}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="34.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46200</v>
+      </c>
+      <c r="H2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E3A8B-70FE-492A-84C5-92052BAE3D69}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7319697-A3B5-46BC-A07E-C0F9D25BB2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABFB85F-97F4-4CF2-B5C4-98CCFE570503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="7" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="InvitationItems" sheetId="19" r:id="rId14"/>
     <sheet name="WorkPermits" sheetId="20" r:id="rId15"/>
     <sheet name="WorkPermitItems" sheetId="21" r:id="rId16"/>
-    <sheet name="WorkPermitItemCities" sheetId="22" r:id="rId17"/>
+    <sheet name="Visas" sheetId="22" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="137">
   <si>
     <t>aýaly</t>
   </si>
@@ -438,7 +438,34 @@
     <t>AS000045</t>
   </si>
   <si>
-    <t>Akbudaý etraby</t>
+    <t>Visa Number</t>
+  </si>
+  <si>
+    <t>Has Invitation</t>
+  </si>
+  <si>
+    <t>Has Border Zone</t>
+  </si>
+  <si>
+    <t>Issued Place</t>
+  </si>
+  <si>
+    <t>Application Item</t>
+  </si>
+  <si>
+    <t>Invitation Item</t>
+  </si>
+  <si>
+    <t>V00003</t>
+  </si>
+  <si>
+    <t>Ankara</t>
+  </si>
+  <si>
+    <t>John Doe - TRM-2026-1</t>
+  </si>
+  <si>
+    <t>John Doe - INV0001</t>
   </si>
 </sst>
 </file>
@@ -1476,27 +1503,100 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E3A8B-70FE-492A-84C5-92052BAE3D69}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.90625" customWidth="1"/>
     <col min="2" max="2" width="17.7265625" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" customWidth="1"/>
+    <col min="12" max="12" width="27.08984375" customWidth="1"/>
+    <col min="13" max="13" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>127</v>
+        <v>133</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46109</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46293</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -1,35 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABFB85F-97F4-4CF2-B5C4-98CCFE570503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57423998-EEA6-4E27-861C-2C1B0C914593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="6" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Persons" sheetId="2" r:id="rId1"/>
-    <sheet name="Passports" sheetId="7" r:id="rId2"/>
-    <sheet name="Education" sheetId="8" r:id="rId3"/>
-    <sheet name="MedicalRecords" sheetId="9" r:id="rId4"/>
-    <sheet name="Lodging" sheetId="10" r:id="rId5"/>
-    <sheet name="AddressOfResidence" sheetId="11" r:id="rId6"/>
-    <sheet name="PositionHistory" sheetId="12" r:id="rId7"/>
-    <sheet name="EmployeeContracts" sheetId="13" r:id="rId8"/>
-    <sheet name="CompanyHead" sheetId="14" r:id="rId9"/>
-    <sheet name="Representative" sheetId="15" r:id="rId10"/>
-    <sheet name="Applications" sheetId="16" r:id="rId11"/>
-    <sheet name="ApplicationItems" sheetId="17" r:id="rId12"/>
-    <sheet name="Invitations" sheetId="18" r:id="rId13"/>
-    <sheet name="InvitationItems" sheetId="19" r:id="rId14"/>
-    <sheet name="WorkPermits" sheetId="20" r:id="rId15"/>
-    <sheet name="WorkPermitItems" sheetId="21" r:id="rId16"/>
-    <sheet name="Visas" sheetId="22" r:id="rId17"/>
+    <sheet name="Persons (2)" sheetId="24" state="hidden" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="23" r:id="rId2"/>
+    <sheet name="Persons" sheetId="2" r:id="rId3"/>
+    <sheet name="Passports" sheetId="7" r:id="rId4"/>
+    <sheet name="Education" sheetId="8" r:id="rId5"/>
+    <sheet name="MedicalRecords" sheetId="9" r:id="rId6"/>
+    <sheet name="Lodging" sheetId="10" r:id="rId7"/>
+    <sheet name="AddressOfResidence" sheetId="11" r:id="rId8"/>
+    <sheet name="PositionHistory" sheetId="12" r:id="rId9"/>
+    <sheet name="EmployeeContracts" sheetId="13" r:id="rId10"/>
+    <sheet name="CompanyHead" sheetId="14" r:id="rId11"/>
+    <sheet name="Representative" sheetId="15" r:id="rId12"/>
+    <sheet name="Applications" sheetId="16" r:id="rId13"/>
+    <sheet name="ApplicationItems" sheetId="17" r:id="rId14"/>
+    <sheet name="Invitations" sheetId="18" r:id="rId15"/>
+    <sheet name="InvitationItems" sheetId="19" r:id="rId16"/>
+    <sheet name="WorkPermits" sheetId="20" r:id="rId17"/>
+    <sheet name="WorkPermitItems" sheetId="21" r:id="rId18"/>
+    <sheet name="Visas" sheetId="22" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -55,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="149">
   <si>
     <t>aýaly</t>
   </si>
@@ -466,18 +468,62 @@
   </si>
   <si>
     <t>John Doe - INV0001</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>DependsOn</t>
+  </si>
+  <si>
+    <t>AnchorEntity</t>
+  </si>
+  <si>
+    <t>AnchorKey</t>
+  </si>
+  <si>
+    <t>AnchorValue</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Company and contracts</t>
+  </si>
+  <si>
+    <t>InvitationScenario</t>
+  </si>
+  <si>
+    <t>Person A full invitation flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario </t>
+  </si>
+  <si>
+    <t>fmscenario</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -571,23 +617,27 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -870,172 +920,179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18289B1E-BB40-4235-8E6A-EF150566973D}">
-  <dimension ref="A1:T3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{284EAD85-AC87-4DC3-9998-07FF8DA54907}">
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.7265625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="1"/>
-    <col min="9" max="9" width="14.6328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.08984375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7265625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.90625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="17.1796875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="18.7265625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="13" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="14.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.08984375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6328125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.90625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.81640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1796875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="18.7265625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:21" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="5">
+      <c r="D2" s="5">
         <v>31121</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="2" t="b">
+      <c r="N2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" s="2" t="b">
+      <c r="O2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>5</v>
@@ -1044,33 +1101,36 @@
         <v>5</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="M3" s="2" t="b">
-        <v>0</v>
       </c>
       <c r="N3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2" t="s">
+      <c r="O3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="2"/>
+      <c r="T3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{E5DA591D-A632-442C-BFE5-07BBE2214744}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{EA5BCE19-030F-4E28-9DBF-39CA34B900F6}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{9E397896-003C-4D63-85F3-6E21620E0353}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{79EE7170-6B29-4196-96AE-B365943EA3CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -1080,34 +1140,56 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8924C1-D194-4DF1-A42A-3D3D75E0E381}">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BD487E-2A04-4D39-924D-AA315766A8E7}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.90625" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="34.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>26</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="b">
-        <v>0</v>
+      <c r="C2" s="7">
+        <v>44134</v>
+      </c>
+      <c r="D2">
+        <v>10000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1116,120 +1198,48 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A61E3F-9A82-457E-8587-FCB3F1FC8E8F}">
-  <dimension ref="A1:Q2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B9BD19-C4E6-4DD0-A060-40ED3F97C71A}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" customWidth="1"/>
-    <col min="7" max="7" width="21.90625" customWidth="1"/>
-    <col min="8" max="8" width="16.36328125" customWidth="1"/>
-    <col min="9" max="9" width="19.54296875" customWidth="1"/>
-    <col min="10" max="10" width="22.6328125" customWidth="1"/>
-    <col min="11" max="11" width="12.90625" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" customWidth="1"/>
-    <col min="14" max="14" width="12.453125" customWidth="1"/>
-    <col min="15" max="15" width="13.7265625" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="35.26953125" customWidth="1"/>
+    <col min="5" max="5" width="23.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="7">
-        <v>46107</v>
-      </c>
-      <c r="E2">
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M2" t="s">
-        <v>110</v>
-      </c>
-      <c r="N2" t="s">
-        <v>111</v>
-      </c>
-      <c r="O2" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1238,28 +1248,41 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38529E09-C163-4F91-A321-7C547851DA34}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8924C1-D194-4DF1-A42A-3D3D75E0E381}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>113</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>114</v>
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1268,50 +1291,127 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED124FB3-4077-4682-BFCE-D98F2F0089BC}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A61E3F-9A82-457E-8587-FCB3F1FC8E8F}">
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="6" max="6" width="13.08984375" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="8" max="8" width="21.90625" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="15.90625" customWidth="1"/>
+    <col min="14" max="14" width="15.1796875" customWidth="1"/>
+    <col min="15" max="15" width="12.453125" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" t="s">
+    <row r="1" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="7">
-        <v>46108</v>
+      <c r="H1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
+        <v>106</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" t="s">
+        <v>109</v>
+      </c>
+      <c r="N2" t="s">
+        <v>110</v>
+      </c>
+      <c r="O2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1320,50 +1420,35 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18967DE7-069E-4DE5-89BC-8EF82DB3AC0C}">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38529E09-C163-4F91-A321-7C547851DA34}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" customWidth="1"/>
-    <col min="6" max="6" width="11.08984375" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>115</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>117</v>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="B2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1372,39 +1457,57 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2AFAE0-31A3-4E30-9723-0089076DBD4C}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED124FB3-4077-4682-BFCE-D98F2F0089BC}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" customWidth="1"/>
-    <col min="4" max="4" width="17.90625" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>120</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="7">
         <v>46108</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1413,31 +1516,25 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976BFC1-7B18-4C48-8C10-5F11DE69F168}">
-  <dimension ref="A1:L2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18967DE7-069E-4DE5-89BC-8EF82DB3AC0C}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="34.7265625" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" customWidth="1"/>
-    <col min="7" max="7" width="16.90625" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="11.26953125" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>120</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C1" t="s">
         <v>47</v>
@@ -1446,54 +1543,30 @@
         <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>121</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G2" s="7">
-        <v>46200</v>
-      </c>
-      <c r="H2" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1502,100 +1575,251 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E3A8B-70FE-492A-84C5-92052BAE3D69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2AFAE0-31A3-4E30-9723-0089076DBD4C}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976BFC1-7B18-4C48-8C10-5F11DE69F168}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="2" max="2" width="17.7265625" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="17.6328125" customWidth="1"/>
-    <col min="12" max="12" width="27.08984375" customWidth="1"/>
-    <col min="13" max="13" width="19.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" customWidth="1"/>
+    <col min="6" max="6" width="34.7265625" customWidth="1"/>
+    <col min="7" max="7" width="16.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.90625" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="11.26953125" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46108</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46200</v>
+      </c>
+      <c r="I2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E3A8B-70FE-492A-84C5-92052BAE3D69}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" customWidth="1"/>
+    <col min="12" max="12" width="17.6328125" customWidth="1"/>
+    <col min="13" max="13" width="27.08984375" customWidth="1"/>
+    <col min="14" max="14" width="19.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>128</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>103</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>99</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>130</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>131</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="7">
+      <c r="C2" s="7">
         <v>46108</v>
       </c>
-      <c r="C2" s="7">
+      <c r="D2" s="7">
         <v>46109</v>
       </c>
-      <c r="D2" s="7">
+      <c r="E2" s="7">
         <v>46293</v>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>112</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>109</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>134</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>50</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>135</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1605,186 +1829,316 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5152DCD-503E-46B6-A0B0-6ACE78ACAC5D}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.36328125" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" customWidth="1"/>
-    <col min="6" max="6" width="16.7265625" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" customWidth="1"/>
-    <col min="8" max="8" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="32.90625" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" customWidth="1"/>
+    <col min="7" max="7" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="7">
-        <v>43961</v>
-      </c>
-      <c r="E2" s="7">
-        <v>47644</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" t="s">
-        <v>54</v>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{C1F98F99-24D1-46F4-B6BB-C2966CD69F8D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8908F50A-91BA-4FB7-ACAF-C045C8FDC603}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18289B1E-BB40-4235-8E6A-EF150566973D}">
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.54296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="14.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.08984375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6328125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.90625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.81640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.1796875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="18.7265625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1" spans="1:21" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5">
+        <v>31121</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
+      <c r="O2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{E5DA591D-A632-442C-BFE5-07BBE2214744}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;9&amp;KFFFF00 Şirket İçi&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B482E7A6-8550-4143-8677-7DF7C1431F64}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A298A566-8EC5-43F3-97A8-8002A58DF513}">
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.36328125" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.1796875" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>64</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="7">
-        <v>46107</v>
-      </c>
-      <c r="C2" s="7">
-        <v>46199</v>
-      </c>
-      <c r="D2" t="b">
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="7">
+        <v>43961</v>
+      </c>
+      <c r="F2" s="7">
+        <v>47644</v>
+      </c>
+      <c r="G2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>68</v>
+      <c r="H2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1793,41 +2147,178 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D0BDE8-D87C-418C-AFC3-DBF6850B63AF}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8908F50A-91BA-4FB7-ACAF-C045C8FDC603}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2">
+        <v>2000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B482E7A6-8550-4143-8677-7DF7C1431F64}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46199</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D0BDE8-D87C-418C-AFC3-DBF6850B63AF}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="27.6328125" customWidth="1"/>
+    <col min="4" max="4" width="22.1796875" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>73</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1837,169 +2328,74 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324BC0BB-CC40-4196-829B-1D1F4666C8A9}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.90625" customWidth="1"/>
-    <col min="3" max="3" width="25.90625" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="20.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="19.7265625" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.90625" customWidth="1"/>
+    <col min="4" max="4" width="25.90625" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="20.26953125" customWidth="1"/>
+    <col min="7" max="7" width="12.90625" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>75</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>76</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>77</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="7">
+      <c r="H2" s="7">
         <v>46107</v>
       </c>
-      <c r="H2" s="7">
+      <c r="I2" s="7">
         <v>46321</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE0BD76-03FB-4C51-8FBE-60A5DA5A106E}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="21.08984375" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="32.08984375" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
-        <v>46107</v>
-      </c>
-      <c r="B2" s="7">
-        <v>47601</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BD487E-2A04-4D39-924D-AA315766A8E7}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="34.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>44134</v>
-      </c>
-      <c r="C2">
-        <v>10000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2008,41 +2404,56 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B9BD19-C4E6-4DD0-A060-40ED3F97C71A}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE0BD76-03FB-4C51-8FBE-60A5DA5A106E}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="35.26953125" customWidth="1"/>
-    <col min="4" max="4" width="23.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21.08984375" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="5" max="5" width="32.08984375" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>90</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="F1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46107</v>
+      </c>
+      <c r="C2" s="7">
+        <v>47601</v>
+      </c>
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
+      <c r="F2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57423998-EEA6-4E27-861C-2C1B0C914593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F103C952-07D2-4031-93F7-867B62608D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons (2)" sheetId="24" state="hidden" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="162">
   <si>
     <t>aýaly</t>
   </si>
@@ -504,6 +504,45 @@
   </si>
   <si>
     <t>fmscenario</t>
+  </si>
+  <si>
+    <t>RegistrationScenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration after invitation	</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>App_Reg_Check_In</t>
+  </si>
+  <si>
+    <t>Türkmenistanyň Döwlet migrasiýa gullugynyň Aşgabat şäheri boýunça müdirliginiň müdirine</t>
+  </si>
+  <si>
+    <t>From City</t>
+  </si>
+  <si>
+    <t>To City</t>
+  </si>
+  <si>
+    <t>TRM-2026-2</t>
+  </si>
+  <si>
+    <t>Travel Date</t>
+  </si>
+  <si>
+    <t>Check Point</t>
+  </si>
+  <si>
+    <t>Purpose of Travel</t>
+  </si>
+  <si>
+    <t>Işlemek üçin</t>
+  </si>
+  <si>
+    <t>Aşgabat şäher howa menzilindäki MGP</t>
   </si>
 </sst>
 </file>
@@ -621,7 +660,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -638,6 +677,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1292,10 +1334,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A61E3F-9A82-457E-8587-FCB3F1FC8E8F}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.90625" customWidth="1"/>
     <col min="2" max="2" width="19.1796875" customWidth="1"/>
     <col min="3" max="3" width="12.6328125" customWidth="1"/>
     <col min="5" max="5" width="9.90625" bestFit="1" customWidth="1"/>
@@ -1306,15 +1348,15 @@
     <col min="10" max="10" width="19.54296875" customWidth="1"/>
     <col min="11" max="11" width="22.6328125" customWidth="1"/>
     <col min="12" max="12" width="12.90625" customWidth="1"/>
-    <col min="13" max="13" width="15.90625" customWidth="1"/>
-    <col min="14" max="14" width="15.1796875" customWidth="1"/>
-    <col min="15" max="15" width="12.453125" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="15.26953125" customWidth="1"/>
+    <col min="13" max="15" width="23.1796875" customWidth="1"/>
+    <col min="16" max="16" width="15.1796875" customWidth="1"/>
+    <col min="17" max="17" width="12.453125" customWidth="1"/>
+    <col min="18" max="18" width="13.7265625" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
@@ -1355,22 +1397,28 @@
         <v>100</v>
       </c>
       <c r="N1" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>145</v>
       </c>
@@ -1404,15 +1452,52 @@
       <c r="L2" t="s">
         <v>109</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>110</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>111</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>112</v>
       </c>
+    </row>
+    <row r="3" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46162</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1421,15 +1506,18 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38529E09-C163-4F91-A321-7C547851DA34}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6328125" customWidth="1"/>
     <col min="2" max="2" width="15.7265625" customWidth="1"/>
     <col min="3" max="3" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="37.81640625" customWidth="1"/>
+    <col min="6" max="6" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
@@ -1439,8 +1527,17 @@
       <c r="C1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>145</v>
       </c>
@@ -1449,6 +1546,26 @@
       </c>
       <c r="C2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7">
+        <v>46112</v>
+      </c>
+      <c r="E3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1830,13 +1947,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5152DCD-503E-46B6-A0B0-6ACE78ACAC5D}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
     <col min="2" max="2" width="21.1796875" customWidth="1"/>
     <col min="3" max="3" width="32.90625" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
     <col min="5" max="5" width="13.7265625" customWidth="1"/>
     <col min="6" max="6" width="14.08984375" customWidth="1"/>
     <col min="7" max="7" width="29.453125" customWidth="1"/>
@@ -1897,6 +2014,23 @@
       </c>
       <c r="G3" s="13" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F103C952-07D2-4031-93F7-867B62608D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46849A0A-D0A4-4BD0-8172-ED4583E088F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons (2)" sheetId="24" state="hidden" r:id="rId1"/>
@@ -27,11 +27,12 @@
     <sheet name="Representative" sheetId="15" r:id="rId12"/>
     <sheet name="Applications" sheetId="16" r:id="rId13"/>
     <sheet name="ApplicationItems" sheetId="17" r:id="rId14"/>
-    <sheet name="Invitations" sheetId="18" r:id="rId15"/>
-    <sheet name="InvitationItems" sheetId="19" r:id="rId16"/>
-    <sheet name="WorkPermits" sheetId="20" r:id="rId17"/>
-    <sheet name="WorkPermitItems" sheetId="21" r:id="rId18"/>
-    <sheet name="Visas" sheetId="22" r:id="rId19"/>
+    <sheet name="Registrations" sheetId="25" r:id="rId15"/>
+    <sheet name="Invitations" sheetId="18" r:id="rId16"/>
+    <sheet name="InvitationItems" sheetId="19" r:id="rId17"/>
+    <sheet name="WorkPermits" sheetId="20" r:id="rId18"/>
+    <sheet name="WorkPermitItems" sheetId="21" r:id="rId19"/>
+    <sheet name="Visas" sheetId="22" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="ApplicationTypeNames">#REF!</definedName>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="162">
   <si>
     <t>aýaly</t>
   </si>
@@ -1506,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38529E09-C163-4F91-A321-7C547851DA34}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.6328125" customWidth="1"/>
@@ -1517,7 +1518,7 @@
     <col min="6" max="6" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
@@ -1527,17 +1528,8 @@
       <c r="C1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>145</v>
       </c>
@@ -1546,26 +1538,6 @@
       </c>
       <c r="C2" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7">
-        <v>46112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1574,6 +1546,64 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A67671B-0E70-4823-BE40-247A43B57F84}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" customWidth="1"/>
+    <col min="5" max="5" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED124FB3-4077-4682-BFCE-D98F2F0089BC}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1632,7 +1662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18967DE7-069E-4DE5-89BC-8EF82DB3AC0C}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1691,7 +1721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2AFAE0-31A3-4E30-9723-0089076DBD4C}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1739,7 +1769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D976BFC1-7B18-4C48-8C10-5F11DE69F168}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1835,7 +1865,103 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5152DCD-503E-46B6-A0B0-6ACE78ACAC5D}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="32.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" customWidth="1"/>
+    <col min="7" max="7" width="29.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{C1F98F99-24D1-46F4-B6BB-C2966CD69F8D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211E3A8B-70FE-492A-84C5-92052BAE3D69}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1941,102 +2067,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5152DCD-503E-46B6-A0B0-6ACE78ACAC5D}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.7265625" customWidth="1"/>
-    <col min="2" max="2" width="21.1796875" customWidth="1"/>
-    <col min="3" max="3" width="32.90625" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" customWidth="1"/>
-    <col min="7" max="7" width="29.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{C1F98F99-24D1-46F4-B6BB-C2966CD69F8D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46849A0A-D0A4-4BD0-8172-ED4583E088F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A6867-3FCF-479E-A5C8-24B6867A18F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="2460" windowWidth="28800" windowHeight="15370" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons (2)" sheetId="24" state="hidden" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="164">
   <si>
     <t>aýaly</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>Aşgabat şäher howa menzilindäki MGP</t>
+  </si>
+  <si>
+    <t>Travel Type</t>
+  </si>
+  <si>
+    <t>ExternalArrival</t>
   </si>
 </sst>
 </file>
@@ -1547,18 +1553,19 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A67671B-0E70-4823-BE40-247A43B57F84}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
-    <col min="5" max="5" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
+    <col min="6" max="6" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
@@ -1569,16 +1576,19 @@
         <v>47</v>
       </c>
       <c r="D1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>158</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -1588,13 +1598,16 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2" s="7">
         <v>46112</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>161</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>160</v>
       </c>
     </row>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A6867-3FCF-479E-A5C8-24B6867A18F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3845CBF4-BC45-4390-AE35-1540A2C7F14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2460" yWindow="2460" windowWidth="28800" windowHeight="15370" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="164">
   <si>
     <t>aýaly</t>
   </si>
@@ -667,7 +667,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -687,6 +687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1553,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A67671B-0E70-4823-BE40-247A43B57F84}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1561,11 +1562,12 @@
     <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.08984375" customWidth="1"/>
     <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="6" max="6" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" customWidth="1"/>
+    <col min="7" max="7" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>147</v>
       </c>
@@ -1582,13 +1584,16 @@
         <v>157</v>
       </c>
       <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
         <v>158</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -1604,10 +1609,13 @@
       <c r="E2" s="7">
         <v>46112</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
         <v>161</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>160</v>
       </c>
     </row>

--- a/Visa2026.DataImporter/data.xlsx
+++ b/Visa2026.DataImporter/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT\source\repos\Visa2026\Visa2026.DataImporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3845CBF4-BC45-4390-AE35-1540A2C7F14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5E081A-223C-497F-83FD-2BB7F41443A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2460" windowWidth="28800" windowHeight="15370" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="28800" windowHeight="15370" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Persons (2)" sheetId="24" state="hidden" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="166">
   <si>
     <t>aýaly</t>
   </si>
@@ -550,6 +550,12 @@
   </si>
   <si>
     <t>ExternalArrival</t>
+  </si>
+  <si>
+    <t>ApplicationScenario</t>
+  </si>
+  <si>
+    <t>All Applications</t>
   </si>
 </sst>
 </file>
@@ -667,7 +673,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -687,7 +693,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1557,7 +1562,7 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" customWidth="1"/>
     <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.08984375" customWidth="1"/>
@@ -1609,7 +1614,7 @@
       <c r="E2" s="7">
         <v>46112</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
       <c r="G2" t="s">
@@ -1888,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5152DCD-503E-46B6-A0B0-6ACE78ACAC5D}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -1972,6 +1977,20 @@
       </c>
       <c r="E4" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
